--- a/recent_30_days_gmv.xlsx
+++ b/recent_30_days_gmv.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuyan/puff/PuffMedia-main/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5390B922-B588-2943-A9E7-CA22EEEC37BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="26860" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="97">
   <si>
     <t>handle</t>
   </si>
@@ -52,6 +58,18 @@
     <t>https://www.tiktok.com/@hallie_grace8/video/7517306682809142558</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@hallie_grace8/video/7522506173505932575</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@hallie_grace8/video/7522309510850022686</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@hallie_grace8/video/7522264807345638687</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@hallie_grace8/video/7522230443303783711</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@hallie_grace8/video/7522184229271244063</t>
   </si>
   <si>
@@ -247,19 +265,10 @@
     <t>https://www.tiktok.com/@hallie_grace8/video/7517036364307762463</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@hallie_grace8/video/7517005346179796255</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@hallie_grace8/video/7516981640749468959</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@hallie_grace8/video/7516948078348356895</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@hallie_grace8/video/7516934263799811358</t>
-  </si>
-  <si>
     <t>2025-06-18</t>
+  </si>
+  <si>
+    <t>2025-07-02</t>
   </si>
   <si>
     <t>2025-07-01</t>
@@ -307,8 +316,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,11 +393,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -430,7 +447,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -462,9 +479,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -496,6 +531,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -671,11 +724,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="82.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -718,28 +775,28 @@
         <v>81</v>
       </c>
       <c r="D2">
-        <v>4300000</v>
+        <v>4500000</v>
       </c>
       <c r="E2">
-        <v>19000</v>
+        <v>19400</v>
       </c>
       <c r="F2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G2">
-        <v>1595</v>
+        <v>1633</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -750,28 +807,28 @@
         <v>82</v>
       </c>
       <c r="D3">
-        <v>892</v>
+        <v>60</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2.58</v>
+        <v>1.67</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -782,28 +839,28 @@
         <v>82</v>
       </c>
       <c r="D4">
-        <v>554</v>
+        <v>18700</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>197</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>3.07</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J4">
-        <v>110.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -814,28 +871,28 @@
         <v>83</v>
       </c>
       <c r="D5">
-        <v>400</v>
+        <v>296</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>7.75</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -846,28 +903,28 @@
         <v>83</v>
       </c>
       <c r="D6">
-        <v>23500</v>
+        <v>431</v>
       </c>
       <c r="E6">
-        <v>469</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>2.32</v>
+        <v>4.41</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -878,28 +935,28 @@
         <v>83</v>
       </c>
       <c r="D7">
-        <v>368</v>
+        <v>4153</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>12.5</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>830.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -907,31 +964,31 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8">
-        <v>2099</v>
+        <v>4699</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>1.67</v>
+        <v>0.7</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>939.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -942,28 +999,28 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>1067</v>
+        <v>448</v>
       </c>
       <c r="E9">
+        <v>26</v>
+      </c>
+      <c r="F9">
         <v>12</v>
-      </c>
-      <c r="F9">
-        <v>6</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>1.69</v>
+        <v>8.48</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>89.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -974,28 +1031,28 @@
         <v>84</v>
       </c>
       <c r="D10">
-        <v>986</v>
+        <v>27400</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>554</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>3.85</v>
+        <v>2.37</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>5480</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1006,28 +1063,28 @@
         <v>84</v>
       </c>
       <c r="D11">
-        <v>1412</v>
+        <v>422</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>1.49</v>
+        <v>11.37</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>84.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1035,31 +1092,31 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12">
-        <v>473</v>
+        <v>3003</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>600.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1067,31 +1124,31 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D13">
-        <v>718</v>
+        <v>1187</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>5.85</v>
+        <v>1.68</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>237.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1099,31 +1156,31 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14">
-        <v>2697</v>
+        <v>1173</v>
       </c>
       <c r="E14">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>2.41</v>
+        <v>3.75</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>234.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1134,10 +1191,10 @@
         <v>85</v>
       </c>
       <c r="D15">
-        <v>526</v>
+        <v>2024</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1146,16 +1203,16 @@
         <v>2</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>3.42</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>404.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1166,28 +1223,28 @@
         <v>85</v>
       </c>
       <c r="D16">
-        <v>9635</v>
+        <v>536</v>
       </c>
       <c r="E16">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0.57</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>107.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1198,28 +1255,28 @@
         <v>85</v>
       </c>
       <c r="D17">
-        <v>5595</v>
+        <v>795</v>
       </c>
       <c r="E17">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0.7</v>
+        <v>5.53</v>
       </c>
       <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -1230,28 +1287,28 @@
         <v>85</v>
       </c>
       <c r="D18">
-        <v>821</v>
+        <v>3059</v>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>5.97</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>611.79999999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1262,28 +1319,28 @@
         <v>86</v>
       </c>
       <c r="D19">
-        <v>13500</v>
+        <v>556</v>
       </c>
       <c r="E19">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0.8100000000000001</v>
+        <v>3.24</v>
       </c>
       <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>111.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1294,28 +1351,28 @@
         <v>86</v>
       </c>
       <c r="D20">
-        <v>3052</v>
+        <v>11300</v>
       </c>
       <c r="E20">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>1.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1326,28 +1383,28 @@
         <v>86</v>
       </c>
       <c r="D21">
-        <v>6594</v>
+        <v>6238</v>
       </c>
       <c r="E21">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>2.81</v>
+        <v>0.63</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>1247.5999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1358,28 +1415,28 @@
         <v>86</v>
       </c>
       <c r="D22">
-        <v>2977</v>
+        <v>1202</v>
       </c>
       <c r="E22">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>1.41</v>
+        <v>4.74</v>
       </c>
       <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>240.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1387,31 +1444,31 @@
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D23">
-        <v>2881</v>
+        <v>14600</v>
       </c>
       <c r="E23">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>1.15</v>
+        <v>0.81</v>
       </c>
       <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1419,31 +1476,31 @@
         <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24">
-        <v>4699</v>
+        <v>3260</v>
       </c>
       <c r="E24">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1451,31 +1508,31 @@
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D25">
-        <v>9282</v>
+        <v>7854</v>
       </c>
       <c r="E25">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0.78</v>
+        <v>2.74</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>1570.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1486,28 +1543,28 @@
         <v>87</v>
       </c>
       <c r="D26">
-        <v>19600</v>
+        <v>3698</v>
       </c>
       <c r="E26">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="F26">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0.68</v>
+        <v>1.38</v>
       </c>
       <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>739.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1518,13 +1575,13 @@
         <v>87</v>
       </c>
       <c r="D27">
-        <v>1892</v>
+        <v>2899</v>
       </c>
       <c r="E27">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1533,13 +1590,13 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>2.64</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="J27">
-        <v>378.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>579.79999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1550,28 +1607,28 @@
         <v>87</v>
       </c>
       <c r="D28">
-        <v>2118</v>
+        <v>4763</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="J28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>952.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1582,28 +1639,28 @@
         <v>87</v>
       </c>
       <c r="D29">
-        <v>89100</v>
+        <v>10300</v>
       </c>
       <c r="E29">
-        <v>1412</v>
+        <v>73</v>
       </c>
       <c r="F29">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>1.7</v>
+        <v>0.79</v>
       </c>
       <c r="J29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1614,28 +1671,28 @@
         <v>88</v>
       </c>
       <c r="D30">
-        <v>1008</v>
+        <v>20200</v>
       </c>
       <c r="E30">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="F30">
+        <v>19</v>
+      </c>
+      <c r="G30">
         <v>6</v>
       </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>3.17</v>
+        <v>0.72</v>
       </c>
       <c r="J30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1646,10 +1703,10 @@
         <v>88</v>
       </c>
       <c r="D31">
-        <v>2230</v>
+        <v>2161</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F31">
         <v>4</v>
@@ -1658,16 +1715,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
       <c r="J31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>432.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1678,28 +1735,28 @@
         <v>88</v>
       </c>
       <c r="D32">
-        <v>692</v>
+        <v>2156</v>
       </c>
       <c r="E32">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>11.99</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="J32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>431.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1710,28 +1767,28 @@
         <v>88</v>
       </c>
       <c r="D33">
-        <v>63300</v>
+        <v>93600</v>
       </c>
       <c r="E33">
-        <v>243</v>
+        <v>1505</v>
       </c>
       <c r="F33">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G33">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>0.45</v>
+        <v>1.72</v>
       </c>
       <c r="J33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>18720</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1739,31 +1796,31 @@
         <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D34">
-        <v>2976</v>
+        <v>1053</v>
       </c>
       <c r="E34">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>1.88</v>
+        <v>3.23</v>
       </c>
       <c r="J34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>210.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -1774,28 +1831,28 @@
         <v>89</v>
       </c>
       <c r="D35">
-        <v>822</v>
+        <v>2336</v>
       </c>
       <c r="E35">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F35">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>6.2</v>
+        <v>1.84</v>
       </c>
       <c r="J35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>467.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -1806,28 +1863,28 @@
         <v>89</v>
       </c>
       <c r="D36">
-        <v>1708</v>
+        <v>696</v>
       </c>
       <c r="E36">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>2.87</v>
+        <v>11.93</v>
       </c>
       <c r="J36">
-        <v>341.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -1838,28 +1895,28 @@
         <v>89</v>
       </c>
       <c r="D37">
-        <v>1615</v>
+        <v>63400</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>244</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>1.61</v>
+        <v>0.45</v>
       </c>
       <c r="J37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>12680</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -1870,28 +1927,28 @@
         <v>89</v>
       </c>
       <c r="D38">
-        <v>580200</v>
+        <v>3158</v>
       </c>
       <c r="E38">
-        <v>11400</v>
+        <v>49</v>
       </c>
       <c r="F38">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="G38">
-        <v>845</v>
+        <v>4</v>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="J38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>631.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -1899,31 +1956,31 @@
         <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39">
-        <v>17600</v>
+        <v>834</v>
       </c>
       <c r="E39">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="F39">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G39">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>1.24</v>
+        <v>6.12</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -1931,31 +1988,31 @@
         <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D40">
-        <v>2073</v>
+        <v>1774</v>
       </c>
       <c r="E40">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F40">
         <v>6</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="J40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>354.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -1963,31 +2020,31 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D41">
-        <v>6169</v>
+        <v>1626</v>
       </c>
       <c r="E41">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="F41">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>325.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -1998,28 +2055,28 @@
         <v>90</v>
       </c>
       <c r="D42">
-        <v>7976</v>
+        <v>591200</v>
       </c>
       <c r="E42">
-        <v>44</v>
+        <v>11600</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>860</v>
       </c>
       <c r="H42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>0.7</v>
+        <v>2.12</v>
       </c>
       <c r="J42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>118240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -2030,28 +2087,28 @@
         <v>90</v>
       </c>
       <c r="D43">
-        <v>16300</v>
+        <v>18300</v>
       </c>
       <c r="E43">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="F43">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0.52</v>
+        <v>1.21</v>
       </c>
       <c r="J43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -2062,28 +2119,28 @@
         <v>90</v>
       </c>
       <c r="D44">
-        <v>43400</v>
+        <v>2111</v>
       </c>
       <c r="E44">
-        <v>545</v>
+        <v>35</v>
       </c>
       <c r="F44">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>1.49</v>
+        <v>2.08</v>
       </c>
       <c r="J44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>422.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -2094,28 +2151,28 @@
         <v>90</v>
       </c>
       <c r="D45">
-        <v>14500</v>
+        <v>6203</v>
       </c>
       <c r="E45">
-        <v>343</v>
+        <v>93</v>
       </c>
       <c r="F45">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G45">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>2.61</v>
+        <v>1.81</v>
       </c>
       <c r="J45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>1240.5999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -2123,31 +2180,31 @@
         <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46">
-        <v>17700</v>
+        <v>8332</v>
       </c>
       <c r="E46">
         <v>44</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>0.28</v>
+        <v>0.67</v>
       </c>
       <c r="J46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>1666.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -2158,28 +2215,28 @@
         <v>91</v>
       </c>
       <c r="D47">
-        <v>4922</v>
+        <v>23000</v>
       </c>
       <c r="E47">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="F47">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="J47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -2190,28 +2247,28 @@
         <v>91</v>
       </c>
       <c r="D48">
-        <v>2861</v>
+        <v>45200</v>
       </c>
       <c r="E48">
-        <v>92</v>
+        <v>558</v>
       </c>
       <c r="F48">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="G48">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>3.7</v>
+        <v>1.46</v>
       </c>
       <c r="J48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>9040</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2222,28 +2279,28 @@
         <v>91</v>
       </c>
       <c r="D49">
-        <v>4071</v>
+        <v>14900</v>
       </c>
       <c r="E49">
-        <v>132</v>
+        <v>353</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>3.44</v>
+        <v>2.62</v>
       </c>
       <c r="J49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -2254,28 +2311,28 @@
         <v>91</v>
       </c>
       <c r="D50">
-        <v>3559</v>
+        <v>18000</v>
       </c>
       <c r="E50">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F50">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
       <c r="H50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>1.55</v>
+        <v>0.27</v>
       </c>
       <c r="J50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -2286,28 +2343,28 @@
         <v>92</v>
       </c>
       <c r="D51">
-        <v>1620</v>
+        <v>5215</v>
       </c>
       <c r="E51">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>3.27</v>
+        <v>0.98</v>
       </c>
       <c r="J51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -2318,28 +2375,28 @@
         <v>92</v>
       </c>
       <c r="D52">
-        <v>861</v>
+        <v>3139</v>
       </c>
       <c r="E52">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="F52">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>5.81</v>
+        <v>3.54</v>
       </c>
       <c r="J52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>627.79999999999995</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -2350,28 +2407,28 @@
         <v>92</v>
       </c>
       <c r="D53">
-        <v>1700000</v>
+        <v>4111</v>
       </c>
       <c r="E53">
-        <v>19100</v>
+        <v>135</v>
       </c>
       <c r="F53">
-        <v>183</v>
+        <v>6</v>
       </c>
       <c r="G53">
-        <v>2488</v>
+        <v>2</v>
       </c>
       <c r="H53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>1.28</v>
+        <v>3.48</v>
       </c>
       <c r="J53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>822.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -2382,28 +2439,28 @@
         <v>92</v>
       </c>
       <c r="D54">
-        <v>1658</v>
+        <v>3638</v>
       </c>
       <c r="E54">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>2.77</v>
+        <v>1.57</v>
       </c>
       <c r="J54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>727.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -2414,28 +2471,28 @@
         <v>93</v>
       </c>
       <c r="D55">
-        <v>81400</v>
+        <v>1623</v>
       </c>
       <c r="E55">
-        <v>342</v>
+        <v>43</v>
       </c>
       <c r="F55">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55">
-        <v>0.48</v>
+        <v>3.27</v>
       </c>
       <c r="J55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>324.60000000000002</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -2446,28 +2503,28 @@
         <v>93</v>
       </c>
       <c r="D56">
-        <v>4408</v>
+        <v>869</v>
       </c>
       <c r="E56">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F56">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>1.43</v>
+        <v>5.75</v>
       </c>
       <c r="J56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <v>173.8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -2478,28 +2535,28 @@
         <v>93</v>
       </c>
       <c r="D57">
-        <v>56900</v>
+        <v>1700000</v>
       </c>
       <c r="E57">
-        <v>160</v>
+        <v>19200</v>
       </c>
       <c r="F57">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="G57">
-        <v>30</v>
+        <v>2505</v>
       </c>
       <c r="H57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>0.36</v>
+        <v>1.29</v>
       </c>
       <c r="J57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -2510,28 +2567,28 @@
         <v>93</v>
       </c>
       <c r="D58">
-        <v>902</v>
+        <v>1669</v>
       </c>
       <c r="E58">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="J58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>333.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -2542,28 +2599,28 @@
         <v>94</v>
       </c>
       <c r="D59">
-        <v>5752</v>
+        <v>81700</v>
       </c>
       <c r="E59">
-        <v>90</v>
+        <v>344</v>
       </c>
       <c r="F59">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>1.86</v>
+        <v>0.48</v>
       </c>
       <c r="J59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>16340</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -2574,28 +2631,28 @@
         <v>94</v>
       </c>
       <c r="D60">
-        <v>1547</v>
+        <v>4476</v>
       </c>
       <c r="E60">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="J60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+        <v>895.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -2606,28 +2663,28 @@
         <v>94</v>
       </c>
       <c r="D61">
-        <v>2887</v>
+        <v>57900</v>
       </c>
       <c r="E61">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>1.77</v>
+        <v>0.35</v>
       </c>
       <c r="J61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>11580</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -2635,31 +2692,31 @@
         <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D62">
-        <v>1555</v>
+        <v>912</v>
       </c>
       <c r="E62">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="J62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>182.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -2667,31 +2724,31 @@
         <v>72</v>
       </c>
       <c r="C63" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D63">
-        <v>4979</v>
+        <v>5902</v>
       </c>
       <c r="E63">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F63">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>0.5600000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="J63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>1180.4000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -2699,31 +2756,31 @@
         <v>73</v>
       </c>
       <c r="C64" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D64">
-        <v>1937</v>
+        <v>1559</v>
       </c>
       <c r="E64">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>2.37</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="J64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>311.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -2731,31 +2788,31 @@
         <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D65">
-        <v>806</v>
+        <v>2978</v>
       </c>
       <c r="E65">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>4.22</v>
+        <v>1.71</v>
       </c>
       <c r="J65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+        <v>595.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -2766,28 +2823,28 @@
         <v>81</v>
       </c>
       <c r="D66">
-        <v>3534</v>
+        <v>1733</v>
       </c>
       <c r="E66">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F66">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>1.75</v>
+        <v>2.89</v>
       </c>
       <c r="J66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
+        <v>346.6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -2795,31 +2852,31 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D67">
-        <v>1805</v>
+        <v>5023</v>
       </c>
       <c r="E67">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>1.99</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="J67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+        <v>1004.6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>10</v>
       </c>
@@ -2827,13 +2884,13 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D68">
-        <v>2121</v>
+        <v>1940</v>
       </c>
       <c r="E68">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F68">
         <v>7</v>
@@ -2842,16 +2899,16 @@
         <v>1</v>
       </c>
       <c r="H68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="J68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -2859,31 +2916,31 @@
         <v>78</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D69">
-        <v>133700</v>
+        <v>820</v>
       </c>
       <c r="E69">
-        <v>1348</v>
+        <v>28</v>
       </c>
       <c r="F69">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G69">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>1.09</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="J69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -2891,31 +2948,31 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D70">
-        <v>197300</v>
+        <v>3628</v>
       </c>
       <c r="E70">
-        <v>1705</v>
+        <v>43</v>
       </c>
       <c r="F70">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="G70">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="H70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70">
-        <v>0.96</v>
+        <v>1.71</v>
       </c>
       <c r="J70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>725.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -2923,102 +2980,102 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D71">
-        <v>4111</v>
+        <v>2238</v>
       </c>
       <c r="E71">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="F71">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>447.6</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" r:id="rId5"/>
-    <hyperlink ref="B7" r:id="rId6"/>
-    <hyperlink ref="B8" r:id="rId7"/>
-    <hyperlink ref="B9" r:id="rId8"/>
-    <hyperlink ref="B10" r:id="rId9"/>
-    <hyperlink ref="B11" r:id="rId10"/>
-    <hyperlink ref="B12" r:id="rId11"/>
-    <hyperlink ref="B13" r:id="rId12"/>
-    <hyperlink ref="B14" r:id="rId13"/>
-    <hyperlink ref="B15" r:id="rId14"/>
-    <hyperlink ref="B16" r:id="rId15"/>
-    <hyperlink ref="B17" r:id="rId16"/>
-    <hyperlink ref="B18" r:id="rId17"/>
-    <hyperlink ref="B19" r:id="rId18"/>
-    <hyperlink ref="B20" r:id="rId19"/>
-    <hyperlink ref="B21" r:id="rId20"/>
-    <hyperlink ref="B22" r:id="rId21"/>
-    <hyperlink ref="B23" r:id="rId22"/>
-    <hyperlink ref="B24" r:id="rId23"/>
-    <hyperlink ref="B25" r:id="rId24"/>
-    <hyperlink ref="B26" r:id="rId25"/>
-    <hyperlink ref="B27" r:id="rId26"/>
-    <hyperlink ref="B28" r:id="rId27"/>
-    <hyperlink ref="B29" r:id="rId28"/>
-    <hyperlink ref="B30" r:id="rId29"/>
-    <hyperlink ref="B31" r:id="rId30"/>
-    <hyperlink ref="B32" r:id="rId31"/>
-    <hyperlink ref="B33" r:id="rId32"/>
-    <hyperlink ref="B34" r:id="rId33"/>
-    <hyperlink ref="B35" r:id="rId34"/>
-    <hyperlink ref="B36" r:id="rId35"/>
-    <hyperlink ref="B37" r:id="rId36"/>
-    <hyperlink ref="B38" r:id="rId37"/>
-    <hyperlink ref="B39" r:id="rId38"/>
-    <hyperlink ref="B40" r:id="rId39"/>
-    <hyperlink ref="B41" r:id="rId40"/>
-    <hyperlink ref="B42" r:id="rId41"/>
-    <hyperlink ref="B43" r:id="rId42"/>
-    <hyperlink ref="B44" r:id="rId43"/>
-    <hyperlink ref="B45" r:id="rId44"/>
-    <hyperlink ref="B46" r:id="rId45"/>
-    <hyperlink ref="B47" r:id="rId46"/>
-    <hyperlink ref="B48" r:id="rId47"/>
-    <hyperlink ref="B49" r:id="rId48"/>
-    <hyperlink ref="B50" r:id="rId49"/>
-    <hyperlink ref="B51" r:id="rId50"/>
-    <hyperlink ref="B52" r:id="rId51"/>
-    <hyperlink ref="B53" r:id="rId52"/>
-    <hyperlink ref="B54" r:id="rId53"/>
-    <hyperlink ref="B55" r:id="rId54"/>
-    <hyperlink ref="B56" r:id="rId55"/>
-    <hyperlink ref="B57" r:id="rId56"/>
-    <hyperlink ref="B58" r:id="rId57"/>
-    <hyperlink ref="B59" r:id="rId58"/>
-    <hyperlink ref="B60" r:id="rId59"/>
-    <hyperlink ref="B61" r:id="rId60"/>
-    <hyperlink ref="B62" r:id="rId61"/>
-    <hyperlink ref="B63" r:id="rId62"/>
-    <hyperlink ref="B64" r:id="rId63"/>
-    <hyperlink ref="B65" r:id="rId64"/>
-    <hyperlink ref="B66" r:id="rId65"/>
-    <hyperlink ref="B67" r:id="rId66"/>
-    <hyperlink ref="B68" r:id="rId67"/>
-    <hyperlink ref="B69" r:id="rId68"/>
-    <hyperlink ref="B70" r:id="rId69"/>
-    <hyperlink ref="B71" r:id="rId70"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="B29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="B32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="B37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="B48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="B52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="B56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="B58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="B61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="B65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/recent_30_days_gmv.xlsx
+++ b/recent_30_days_gmv.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuyan/puff/PuffMedia-main/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5390B922-B588-2943-A9E7-CA22EEEC37BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="26860" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="96">
   <si>
     <t>handle</t>
   </si>
@@ -58,6 +52,9 @@
     <t>https://www.tiktok.com/@hallie_grace8/video/7517306682809142558</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@hallie_grace8/video/7522548539545767199</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@hallie_grace8/video/7522506173505932575</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
     <t>https://www.tiktok.com/@hallie_grace8/video/7517331539479285023</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@hallie_grace8/video/7517036364307762463</t>
-  </si>
-  <si>
     <t>2025-06-18</t>
   </si>
   <si>
@@ -308,16 +302,13 @@
   </si>
   <si>
     <t>2025-06-19</t>
-  </si>
-  <si>
-    <t>2025-06-17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,19 +384,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -447,7 +430,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -479,27 +462,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -531,24 +496,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -724,15 +671,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="82.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -764,7 +707,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -781,10 +724,10 @@
         <v>19400</v>
       </c>
       <c r="F2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G2">
-        <v>1633</v>
+        <v>1640</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -796,7 +739,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -807,7 +750,7 @@
         <v>82</v>
       </c>
       <c r="D3">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -822,13 +765,13 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1.67</v>
+        <v>5.56</v>
       </c>
       <c r="J3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -839,28 +782,28 @@
         <v>82</v>
       </c>
       <c r="D4">
-        <v>18700</v>
+        <v>181</v>
       </c>
       <c r="E4">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1.1299999999999999</v>
+        <v>6.63</v>
       </c>
       <c r="J4">
-        <v>3740</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -868,31 +811,31 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5">
-        <v>296</v>
+        <v>26900</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>339</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>9.8000000000000007</v>
+        <v>1.4</v>
       </c>
       <c r="J5">
-        <v>59.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -903,28 +846,28 @@
         <v>83</v>
       </c>
       <c r="D6">
-        <v>431</v>
+        <v>320</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>4.41</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>86.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -935,28 +878,28 @@
         <v>83</v>
       </c>
       <c r="D7">
-        <v>4153</v>
+        <v>514</v>
       </c>
       <c r="E7">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>2.4300000000000002</v>
+        <v>3.7</v>
       </c>
       <c r="J7">
-        <v>830.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>102.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -967,28 +910,28 @@
         <v>83</v>
       </c>
       <c r="D8">
-        <v>4699</v>
+        <v>4788</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.7</v>
+        <v>2.21</v>
       </c>
       <c r="J8">
-        <v>939.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>957.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -996,31 +939,31 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9">
-        <v>448</v>
+        <v>10800</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>8.48</v>
+        <v>0.39</v>
       </c>
       <c r="J9">
-        <v>89.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1031,28 +974,28 @@
         <v>84</v>
       </c>
       <c r="D10">
-        <v>27400</v>
+        <v>453</v>
       </c>
       <c r="E10">
-        <v>554</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>2.37</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J10">
-        <v>5480</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>90.59999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1063,28 +1006,28 @@
         <v>84</v>
       </c>
       <c r="D11">
-        <v>422</v>
+        <v>28200</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>564</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>11.37</v>
+        <v>2.34</v>
       </c>
       <c r="J11">
-        <v>84.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5640</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1092,16 +1035,16 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12">
-        <v>3003</v>
+        <v>427</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1110,13 +1053,13 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>1.4</v>
+        <v>11.24</v>
       </c>
       <c r="J12">
-        <v>600.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1127,28 +1070,28 @@
         <v>85</v>
       </c>
       <c r="D13">
-        <v>1187</v>
+        <v>3248</v>
       </c>
       <c r="E13">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="J13">
-        <v>237.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>649.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1159,28 +1102,28 @@
         <v>85</v>
       </c>
       <c r="D14">
-        <v>1173</v>
+        <v>1206</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>3.75</v>
+        <v>1.74</v>
       </c>
       <c r="J14">
-        <v>234.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>241.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1191,28 +1134,28 @@
         <v>85</v>
       </c>
       <c r="D15">
-        <v>2024</v>
+        <v>1200</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>1.1399999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="J15">
-        <v>404.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1223,28 +1166,28 @@
         <v>85</v>
       </c>
       <c r="D16">
-        <v>536</v>
+        <v>2128</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>2.4300000000000002</v>
+        <v>1.13</v>
       </c>
       <c r="J16">
-        <v>107.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>425.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1255,28 +1198,28 @@
         <v>85</v>
       </c>
       <c r="D17">
-        <v>795</v>
+        <v>545</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>5.53</v>
+        <v>2.39</v>
       </c>
       <c r="J17">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -1287,28 +1230,28 @@
         <v>85</v>
       </c>
       <c r="D18">
-        <v>3059</v>
+        <v>813</v>
       </c>
       <c r="E18">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>2.2599999999999998</v>
+        <v>5.66</v>
       </c>
       <c r="J18">
-        <v>611.79999999999995</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+        <v>162.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1316,31 +1259,31 @@
         <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19">
-        <v>556</v>
+        <v>3148</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>3.24</v>
+        <v>2.19</v>
       </c>
       <c r="J19">
-        <v>111.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+        <v>629.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1351,28 +1294,28 @@
         <v>86</v>
       </c>
       <c r="D20">
-        <v>11300</v>
+        <v>561</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
         <v>2</v>
       </c>
-      <c r="G20">
-        <v>4</v>
-      </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.57999999999999996</v>
+        <v>3.39</v>
       </c>
       <c r="J20">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>112.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1383,28 +1326,28 @@
         <v>86</v>
       </c>
       <c r="D21">
-        <v>6238</v>
+        <v>11500</v>
       </c>
       <c r="E21">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="J21">
-        <v>1247.5999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1415,28 +1358,28 @@
         <v>86</v>
       </c>
       <c r="D22">
-        <v>1202</v>
+        <v>6341</v>
       </c>
       <c r="E22">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22">
-        <v>4.74</v>
+        <v>0.62</v>
       </c>
       <c r="J22">
-        <v>240.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1268.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1444,31 +1387,31 @@
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D23">
-        <v>14600</v>
+        <v>1282</v>
       </c>
       <c r="E23">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>0.81</v>
+        <v>4.52</v>
       </c>
       <c r="J23">
-        <v>2920</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>256.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1479,28 +1422,28 @@
         <v>87</v>
       </c>
       <c r="D24">
-        <v>3260</v>
+        <v>14700</v>
       </c>
       <c r="E24">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>1.47</v>
+        <v>0.82</v>
       </c>
       <c r="J24">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1511,28 +1454,28 @@
         <v>87</v>
       </c>
       <c r="D25">
-        <v>7854</v>
+        <v>3282</v>
       </c>
       <c r="E25">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>2.74</v>
+        <v>1.46</v>
       </c>
       <c r="J25">
-        <v>1570.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>656.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1543,28 +1486,28 @@
         <v>87</v>
       </c>
       <c r="D26">
-        <v>3698</v>
+        <v>7923</v>
       </c>
       <c r="E26">
-        <v>47</v>
+        <v>205</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1.38</v>
+        <v>2.73</v>
       </c>
       <c r="J26">
-        <v>739.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1584.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1575,13 +1518,13 @@
         <v>87</v>
       </c>
       <c r="D27">
-        <v>2899</v>
+        <v>3949</v>
       </c>
       <c r="E27">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1590,13 +1533,13 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>1.1399999999999999</v>
+        <v>1.47</v>
       </c>
       <c r="J27">
-        <v>579.79999999999995</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>789.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1607,28 +1550,28 @@
         <v>87</v>
       </c>
       <c r="D28">
-        <v>4763</v>
+        <v>2900</v>
       </c>
       <c r="E28">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="J28">
-        <v>952.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1639,28 +1582,28 @@
         <v>87</v>
       </c>
       <c r="D29">
-        <v>10300</v>
+        <v>4769</v>
       </c>
       <c r="E29">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29">
-        <v>0.79</v>
+        <v>1.45</v>
       </c>
       <c r="J29">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>953.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1668,31 +1611,31 @@
         <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D30">
-        <v>20200</v>
+        <v>10500</v>
       </c>
       <c r="E30">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J30">
-        <v>4040</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1703,28 +1646,28 @@
         <v>88</v>
       </c>
       <c r="D31">
-        <v>2161</v>
+        <v>20200</v>
       </c>
       <c r="E31">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>2.41</v>
+        <v>0.72</v>
       </c>
       <c r="J31">
-        <v>432.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1735,28 +1678,28 @@
         <v>88</v>
       </c>
       <c r="D32">
-        <v>2156</v>
+        <v>2189</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>1.1599999999999999</v>
+        <v>2.42</v>
       </c>
       <c r="J32">
-        <v>431.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+        <v>437.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1767,28 +1710,28 @@
         <v>88</v>
       </c>
       <c r="D33">
-        <v>93600</v>
+        <v>2170</v>
       </c>
       <c r="E33">
-        <v>1505</v>
+        <v>18</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="J33">
-        <v>18720</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1796,31 +1739,31 @@
         <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D34">
-        <v>1053</v>
+        <v>94100</v>
       </c>
       <c r="E34">
-        <v>27</v>
+        <v>1515</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>3.23</v>
+        <v>1.72</v>
       </c>
       <c r="J34">
-        <v>210.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+        <v>18820</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -1831,28 +1774,28 @@
         <v>89</v>
       </c>
       <c r="D35">
-        <v>2336</v>
+        <v>1059</v>
       </c>
       <c r="E35">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35">
-        <v>1.84</v>
+        <v>3.21</v>
       </c>
       <c r="J35">
-        <v>467.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+        <v>211.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -1863,28 +1806,28 @@
         <v>89</v>
       </c>
       <c r="D36">
-        <v>696</v>
+        <v>2376</v>
       </c>
       <c r="E36">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="F36">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>11.93</v>
+        <v>1.85</v>
       </c>
       <c r="J36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+        <v>475.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -1895,28 +1838,28 @@
         <v>89</v>
       </c>
       <c r="D37">
-        <v>63400</v>
+        <v>699</v>
       </c>
       <c r="E37">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="F37">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G37">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>0.45</v>
+        <v>11.87</v>
       </c>
       <c r="J37">
-        <v>12680</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -1927,28 +1870,28 @@
         <v>89</v>
       </c>
       <c r="D38">
-        <v>3158</v>
+        <v>63400</v>
       </c>
       <c r="E38">
-        <v>49</v>
+        <v>244</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1.84</v>
+        <v>0.46</v>
       </c>
       <c r="J38">
-        <v>631.6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+        <v>12680</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -1956,31 +1899,31 @@
         <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D39">
-        <v>834</v>
+        <v>3194</v>
       </c>
       <c r="E39">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F39">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>6.12</v>
+        <v>1.82</v>
       </c>
       <c r="J39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+        <v>638.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -1991,28 +1934,28 @@
         <v>90</v>
       </c>
       <c r="D40">
-        <v>1774</v>
+        <v>838</v>
       </c>
       <c r="E40">
         <v>41</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>2.76</v>
+        <v>6.09</v>
       </c>
       <c r="J40">
-        <v>354.8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -2023,28 +1966,28 @@
         <v>90</v>
       </c>
       <c r="D41">
-        <v>1626</v>
+        <v>1786</v>
       </c>
       <c r="E41">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J41">
-        <v>325.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+        <v>357.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -2055,28 +1998,28 @@
         <v>90</v>
       </c>
       <c r="D42">
-        <v>591200</v>
+        <v>1626</v>
       </c>
       <c r="E42">
-        <v>11600</v>
+        <v>17</v>
       </c>
       <c r="F42">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="G42">
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="J42">
-        <v>118240</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+        <v>325.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -2087,28 +2030,28 @@
         <v>90</v>
       </c>
       <c r="D43">
-        <v>18300</v>
+        <v>592400</v>
       </c>
       <c r="E43">
-        <v>186</v>
+        <v>11700</v>
       </c>
       <c r="F43">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="G43">
-        <v>15</v>
+        <v>862</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>1.21</v>
+        <v>2.14</v>
       </c>
       <c r="J43">
-        <v>3660</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+        <v>118480</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -2119,28 +2062,28 @@
         <v>90</v>
       </c>
       <c r="D44">
-        <v>2111</v>
+        <v>18400</v>
       </c>
       <c r="E44">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>2.08</v>
+        <v>1.21</v>
       </c>
       <c r="J44">
-        <v>422.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -2151,28 +2094,28 @@
         <v>90</v>
       </c>
       <c r="D45">
-        <v>6203</v>
+        <v>2116</v>
       </c>
       <c r="E45">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="F45">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="J45">
-        <v>1240.5999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+        <v>423.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -2180,31 +2123,31 @@
         <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46">
-        <v>8332</v>
+        <v>6207</v>
       </c>
       <c r="E46">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="F46">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46">
-        <v>0.67</v>
+        <v>1.8</v>
       </c>
       <c r="J46">
-        <v>1666.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1241.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -2215,13 +2158,13 @@
         <v>91</v>
       </c>
       <c r="D47">
-        <v>23000</v>
+        <v>8382</v>
       </c>
       <c r="E47">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -2230,13 +2173,13 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="J47">
-        <v>4600</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1676.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -2247,28 +2190,28 @@
         <v>91</v>
       </c>
       <c r="D48">
-        <v>45200</v>
+        <v>26100</v>
       </c>
       <c r="E48">
-        <v>558</v>
+        <v>96</v>
       </c>
       <c r="F48">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="G48">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>1.46</v>
+        <v>0.42</v>
       </c>
       <c r="J48">
-        <v>9040</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2279,28 +2222,28 @@
         <v>91</v>
       </c>
       <c r="D49">
-        <v>14900</v>
+        <v>45600</v>
       </c>
       <c r="E49">
-        <v>353</v>
+        <v>563</v>
       </c>
       <c r="F49">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="G49">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="J49">
-        <v>2980</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+        <v>9120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -2311,28 +2254,28 @@
         <v>91</v>
       </c>
       <c r="D50">
-        <v>18000</v>
+        <v>14900</v>
       </c>
       <c r="E50">
-        <v>44</v>
+        <v>353</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>0.27</v>
+        <v>2.62</v>
       </c>
       <c r="J50">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -2340,16 +2283,16 @@
         <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D51">
-        <v>5215</v>
+        <v>18000</v>
       </c>
       <c r="E51">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F51">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -2358,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>0.98</v>
+        <v>0.28</v>
       </c>
       <c r="J51">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -2375,28 +2318,28 @@
         <v>92</v>
       </c>
       <c r="D52">
-        <v>3139</v>
+        <v>5239</v>
       </c>
       <c r="E52">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G52">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>3.54</v>
+        <v>0.97</v>
       </c>
       <c r="J52">
-        <v>627.79999999999995</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1047.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -2407,28 +2350,28 @@
         <v>92</v>
       </c>
       <c r="D53">
-        <v>4111</v>
+        <v>3144</v>
       </c>
       <c r="E53">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="F53">
         <v>6</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
       </c>
       <c r="I53">
-        <v>3.48</v>
+        <v>3.53</v>
       </c>
       <c r="J53">
-        <v>822.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+        <v>628.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -2439,13 +2382,13 @@
         <v>92</v>
       </c>
       <c r="D54">
-        <v>3638</v>
+        <v>4116</v>
       </c>
       <c r="E54">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -2454,13 +2397,13 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="J54">
-        <v>727.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+        <v>823.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -2468,31 +2411,31 @@
         <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D55">
-        <v>1623</v>
+        <v>3640</v>
       </c>
       <c r="E55">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F55">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
       </c>
       <c r="I55">
-        <v>3.27</v>
+        <v>1.57</v>
       </c>
       <c r="J55">
-        <v>324.60000000000002</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -2503,28 +2446,28 @@
         <v>93</v>
       </c>
       <c r="D56">
-        <v>869</v>
+        <v>1625</v>
       </c>
       <c r="E56">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F56">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
       </c>
       <c r="I56">
-        <v>5.75</v>
+        <v>3.26</v>
       </c>
       <c r="J56">
-        <v>173.8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -2535,28 +2478,28 @@
         <v>93</v>
       </c>
       <c r="D57">
-        <v>1700000</v>
+        <v>871</v>
       </c>
       <c r="E57">
-        <v>19200</v>
+        <v>35</v>
       </c>
       <c r="F57">
-        <v>187</v>
+        <v>12</v>
       </c>
       <c r="G57">
-        <v>2505</v>
+        <v>3</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
       </c>
       <c r="I57">
-        <v>1.29</v>
+        <v>5.74</v>
       </c>
       <c r="J57">
-        <v>340000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+        <v>174.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -2567,28 +2510,28 @@
         <v>93</v>
       </c>
       <c r="D58">
-        <v>1669</v>
+        <v>1700000</v>
       </c>
       <c r="E58">
-        <v>38</v>
+        <v>19300</v>
       </c>
       <c r="F58">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>2508</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
       </c>
       <c r="I58">
-        <v>2.76</v>
+        <v>1.29</v>
       </c>
       <c r="J58">
-        <v>333.8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -2596,31 +2539,31 @@
         <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59">
-        <v>81700</v>
+        <v>1669</v>
       </c>
       <c r="E59">
-        <v>344</v>
+        <v>38</v>
       </c>
       <c r="F59">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G59">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
       </c>
       <c r="I59">
-        <v>0.48</v>
+        <v>2.76</v>
       </c>
       <c r="J59">
-        <v>16340</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+        <v>333.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -2631,28 +2574,28 @@
         <v>94</v>
       </c>
       <c r="D60">
-        <v>4476</v>
+        <v>81800</v>
       </c>
       <c r="E60">
-        <v>51</v>
+        <v>344</v>
       </c>
       <c r="F60">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G60">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
       </c>
       <c r="I60">
-        <v>1.43</v>
+        <v>0.48</v>
       </c>
       <c r="J60">
-        <v>895.2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+        <v>16360</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -2663,28 +2606,28 @@
         <v>94</v>
       </c>
       <c r="D61">
-        <v>57900</v>
+        <v>4489</v>
       </c>
       <c r="E61">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="F61">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G61">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>0.35</v>
+        <v>1.43</v>
       </c>
       <c r="J61">
-        <v>11580</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+        <v>897.8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -2695,28 +2638,28 @@
         <v>94</v>
       </c>
       <c r="D62">
-        <v>912</v>
+        <v>58000</v>
       </c>
       <c r="E62">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>2.96</v>
+        <v>0.35</v>
       </c>
       <c r="J62">
-        <v>182.4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -2724,31 +2667,31 @@
         <v>72</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D63">
-        <v>5902</v>
+        <v>914</v>
       </c>
       <c r="E63">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="F63">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
       </c>
       <c r="I63">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="J63">
-        <v>1180.4000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+        <v>182.8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -2759,28 +2702,28 @@
         <v>95</v>
       </c>
       <c r="D64">
-        <v>1559</v>
+        <v>5909</v>
       </c>
       <c r="E64">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="F64">
+        <v>12</v>
+      </c>
+      <c r="G64">
         <v>5</v>
       </c>
-      <c r="G64">
-        <v>3</v>
-      </c>
       <c r="H64" t="b">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>2.1800000000000002</v>
+        <v>1.83</v>
       </c>
       <c r="J64">
-        <v>311.8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1181.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -2791,28 +2734,28 @@
         <v>95</v>
       </c>
       <c r="D65">
-        <v>2978</v>
+        <v>1559</v>
       </c>
       <c r="E65">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65">
         <v>3</v>
       </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
       <c r="H65" t="b">
         <v>1</v>
       </c>
       <c r="I65">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="J65">
-        <v>595.6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+        <v>311.8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -2820,31 +2763,31 @@
         <v>75</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D66">
-        <v>1733</v>
+        <v>2985</v>
       </c>
       <c r="E66">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F66">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>2.89</v>
+        <v>1.71</v>
       </c>
       <c r="J66">
-        <v>346.6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -2855,28 +2798,28 @@
         <v>81</v>
       </c>
       <c r="D67">
-        <v>5023</v>
+        <v>1785</v>
       </c>
       <c r="E67">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F67">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
       </c>
       <c r="I67">
-        <v>0.56000000000000005</v>
+        <v>2.8</v>
       </c>
       <c r="J67">
-        <v>1004.6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>10</v>
       </c>
@@ -2887,28 +2830,28 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>1940</v>
+        <v>5026</v>
       </c>
       <c r="E68">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
       </c>
       <c r="I68">
-        <v>2.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J68">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1005.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -2919,28 +2862,28 @@
         <v>81</v>
       </c>
       <c r="D69">
-        <v>820</v>
+        <v>1941</v>
       </c>
       <c r="E69">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
       </c>
       <c r="I69">
-        <v>4.1500000000000004</v>
+        <v>2.37</v>
       </c>
       <c r="J69">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+        <v>388.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -2951,28 +2894,28 @@
         <v>81</v>
       </c>
       <c r="D70">
-        <v>3628</v>
+        <v>821</v>
       </c>
       <c r="E70">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F70">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>1.71</v>
+        <v>4.14</v>
       </c>
       <c r="J70">
-        <v>725.6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+        <v>164.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -2980,102 +2923,102 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D71">
-        <v>2238</v>
+        <v>3644</v>
       </c>
       <c r="E71">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F71">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
       </c>
       <c r="I71">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="J71">
-        <v>447.6</v>
+        <v>728.8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="B20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="B22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="B29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="B32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="B37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="B48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="B56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="B58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="B61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="B65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B3" r:id="rId2"/>
+    <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" r:id="rId5"/>
+    <hyperlink ref="B7" r:id="rId6"/>
+    <hyperlink ref="B8" r:id="rId7"/>
+    <hyperlink ref="B9" r:id="rId8"/>
+    <hyperlink ref="B10" r:id="rId9"/>
+    <hyperlink ref="B11" r:id="rId10"/>
+    <hyperlink ref="B12" r:id="rId11"/>
+    <hyperlink ref="B13" r:id="rId12"/>
+    <hyperlink ref="B14" r:id="rId13"/>
+    <hyperlink ref="B15" r:id="rId14"/>
+    <hyperlink ref="B16" r:id="rId15"/>
+    <hyperlink ref="B17" r:id="rId16"/>
+    <hyperlink ref="B18" r:id="rId17"/>
+    <hyperlink ref="B19" r:id="rId18"/>
+    <hyperlink ref="B20" r:id="rId19"/>
+    <hyperlink ref="B21" r:id="rId20"/>
+    <hyperlink ref="B22" r:id="rId21"/>
+    <hyperlink ref="B23" r:id="rId22"/>
+    <hyperlink ref="B24" r:id="rId23"/>
+    <hyperlink ref="B25" r:id="rId24"/>
+    <hyperlink ref="B26" r:id="rId25"/>
+    <hyperlink ref="B27" r:id="rId26"/>
+    <hyperlink ref="B28" r:id="rId27"/>
+    <hyperlink ref="B29" r:id="rId28"/>
+    <hyperlink ref="B30" r:id="rId29"/>
+    <hyperlink ref="B31" r:id="rId30"/>
+    <hyperlink ref="B32" r:id="rId31"/>
+    <hyperlink ref="B33" r:id="rId32"/>
+    <hyperlink ref="B34" r:id="rId33"/>
+    <hyperlink ref="B35" r:id="rId34"/>
+    <hyperlink ref="B36" r:id="rId35"/>
+    <hyperlink ref="B37" r:id="rId36"/>
+    <hyperlink ref="B38" r:id="rId37"/>
+    <hyperlink ref="B39" r:id="rId38"/>
+    <hyperlink ref="B40" r:id="rId39"/>
+    <hyperlink ref="B41" r:id="rId40"/>
+    <hyperlink ref="B42" r:id="rId41"/>
+    <hyperlink ref="B43" r:id="rId42"/>
+    <hyperlink ref="B44" r:id="rId43"/>
+    <hyperlink ref="B45" r:id="rId44"/>
+    <hyperlink ref="B46" r:id="rId45"/>
+    <hyperlink ref="B47" r:id="rId46"/>
+    <hyperlink ref="B48" r:id="rId47"/>
+    <hyperlink ref="B49" r:id="rId48"/>
+    <hyperlink ref="B50" r:id="rId49"/>
+    <hyperlink ref="B51" r:id="rId50"/>
+    <hyperlink ref="B52" r:id="rId51"/>
+    <hyperlink ref="B53" r:id="rId52"/>
+    <hyperlink ref="B54" r:id="rId53"/>
+    <hyperlink ref="B55" r:id="rId54"/>
+    <hyperlink ref="B56" r:id="rId55"/>
+    <hyperlink ref="B57" r:id="rId56"/>
+    <hyperlink ref="B58" r:id="rId57"/>
+    <hyperlink ref="B59" r:id="rId58"/>
+    <hyperlink ref="B60" r:id="rId59"/>
+    <hyperlink ref="B61" r:id="rId60"/>
+    <hyperlink ref="B62" r:id="rId61"/>
+    <hyperlink ref="B63" r:id="rId62"/>
+    <hyperlink ref="B64" r:id="rId63"/>
+    <hyperlink ref="B65" r:id="rId64"/>
+    <hyperlink ref="B66" r:id="rId65"/>
+    <hyperlink ref="B67" r:id="rId66"/>
+    <hyperlink ref="B68" r:id="rId67"/>
+    <hyperlink ref="B69" r:id="rId68"/>
+    <hyperlink ref="B70" r:id="rId69"/>
+    <hyperlink ref="B71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
